--- a/data/trans_orig/IMC_inf_MED_R3-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IMC_inf_MED_R3-Edad-trans_orig.xlsx
@@ -545,7 +545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido en 2012 (tasa de respuesta: 70,03%)</t>
+          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido en 2012 (tasa de respuesta: 83,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -735,61 +735,61 @@
         <v>9296</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>5751</v>
+        <v>5536</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>13983</v>
+        <v>14301</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.353100093784024</v>
+        <v>0.2686559845479436</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.2184204763422358</v>
+        <v>0.1599739288085548</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.5311005973805584</v>
+        <v>0.4132773314989224</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>11106</v>
+        <v>13629</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>7129</v>
+        <v>9514</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>15482</v>
+        <v>19562</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.3587649914826891</v>
+        <v>0.3308030712115972</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.2302864169077115</v>
+        <v>0.2309267427224705</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.5001105314986991</v>
+        <v>0.4747917622903206</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>20403</v>
+        <v>22926</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>15211</v>
+        <v>17446</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>26672</v>
+        <v>30299</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.3561614374447974</v>
+        <v>0.3024340882146896</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.2655358624652673</v>
+        <v>0.2301399582391225</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.4656046654836167</v>
+        <v>0.3997005162946713</v>
       </c>
     </row>
     <row r="5">
@@ -800,67 +800,67 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>17032</v>
+        <v>25307</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>12345</v>
+        <v>20302</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>20577</v>
+        <v>29067</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.6468999062159759</v>
+        <v>0.7313440154520563</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.4688994026194415</v>
+        <v>0.5867226685010762</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.7815795236577642</v>
+        <v>0.8400260711914451</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>19851</v>
+        <v>27572</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>15475</v>
+        <v>21639</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>23828</v>
+        <v>31687</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.6412350085173109</v>
+        <v>0.6691969287884028</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.4998894685013008</v>
+        <v>0.5252082377096805</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.7697135830922882</v>
+        <v>0.7690732572775295</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>36882</v>
+        <v>52878</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>30613</v>
+        <v>45505</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>42074</v>
+        <v>58358</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.6438385625552027</v>
+        <v>0.6975659117853104</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.5343953345163829</v>
+        <v>0.6002994837053287</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.7344641375347325</v>
+        <v>0.7698600417608775</v>
       </c>
     </row>
     <row r="6">
@@ -871,16 +871,16 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>26328</v>
+        <v>34603</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>26328</v>
+        <v>34603</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>26328</v>
+        <v>34603</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>1</v>
@@ -892,16 +892,16 @@
         <v>1</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>30957</v>
+        <v>41201</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>30957</v>
+        <v>41201</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>30957</v>
+        <v>41201</v>
       </c>
       <c r="N6" s="6" t="n">
         <v>1</v>
@@ -913,16 +913,16 @@
         <v>1</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>57285</v>
+        <v>75804</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>57285</v>
+        <v>75804</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>57285</v>
+        <v>75804</v>
       </c>
       <c r="U6" s="6" t="n">
         <v>1</v>
@@ -946,67 +946,67 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>92073</v>
+        <v>101028</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>80505</v>
+        <v>87336</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>104930</v>
+        <v>113422</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.4413356370932798</v>
+        <v>0.3928905113032732</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.3858842805109594</v>
+        <v>0.3396439430082163</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.5029640080197219</v>
+        <v>0.4410919871254481</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>60896</v>
+        <v>67686</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>51069</v>
+        <v>56430</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>71519</v>
+        <v>79152</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.3232837334528474</v>
+        <v>0.2976203129174493</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.2711140029350211</v>
+        <v>0.2481260501129461</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.3796787474390996</v>
+        <v>0.348037233982761</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>152969</v>
+        <v>168715</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>137570</v>
+        <v>150782</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>170035</v>
+        <v>186868</v>
       </c>
       <c r="U7" s="6" t="n">
-        <v>0.38532162251763</v>
+        <v>0.3481765574850554</v>
       </c>
       <c r="V7" s="6" t="n">
-        <v>0.3465328212126507</v>
+        <v>0.3111683145518659</v>
       </c>
       <c r="W7" s="6" t="n">
-        <v>0.4283103193327163</v>
+        <v>0.3856396188058301</v>
       </c>
     </row>
     <row r="8">
@@ -1017,67 +1017,67 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>163</v>
+        <v>219</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>116551</v>
+        <v>156112</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>103694</v>
+        <v>143718</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>128119</v>
+        <v>169804</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.5586643629067203</v>
+        <v>0.6071094886967268</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.4970359919802781</v>
+        <v>0.5589080128745519</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.6141157194890406</v>
+        <v>0.6603560569917836</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>183</v>
+        <v>230</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>127470</v>
+        <v>159739</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>116847</v>
+        <v>148273</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>137297</v>
+        <v>170995</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.6767162665471527</v>
+        <v>0.7023796870825506</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.6203212525609004</v>
+        <v>0.6519627660172389</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.7288859970649789</v>
+        <v>0.7518739498870537</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>346</v>
+        <v>449</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>244021</v>
+        <v>315851</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>226955</v>
+        <v>297698</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>259420</v>
+        <v>333784</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.61467837748237</v>
+        <v>0.6518234425149446</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.5716896806672837</v>
+        <v>0.6143603811941699</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.6534671787873494</v>
+        <v>0.6888316854481341</v>
       </c>
     </row>
     <row r="9">
@@ -1088,16 +1088,16 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>291</v>
+        <v>358</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>208624</v>
+        <v>257140</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>208624</v>
+        <v>257140</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>208624</v>
+        <v>257140</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
@@ -1109,16 +1109,16 @@
         <v>1</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>270</v>
+        <v>326</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>188366</v>
+        <v>227425</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>188366</v>
+        <v>227425</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>188366</v>
+        <v>227425</v>
       </c>
       <c r="N9" s="6" t="n">
         <v>1</v>
@@ -1130,16 +1130,16 @@
         <v>1</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>561</v>
+        <v>684</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>396990</v>
+        <v>484566</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>396990</v>
+        <v>484566</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>396990</v>
+        <v>484566</v>
       </c>
       <c r="U9" s="6" t="n">
         <v>1</v>
@@ -1163,67 +1163,67 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>33034</v>
+        <v>38411</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>25421</v>
+        <v>30093</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>42324</v>
+        <v>48763</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.2466533911207902</v>
+        <v>0.2434410228568307</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.1898095282830959</v>
+        <v>0.1907223908377931</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.3160145068250873</v>
+        <v>0.3090506764256635</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>29257</v>
+        <v>33471</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>22264</v>
+        <v>24188</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>37293</v>
+        <v>41398</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.2217395663786306</v>
+        <v>0.2142456501107638</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.1687353409103804</v>
+        <v>0.1548277565125789</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.2826403069150239</v>
+        <v>0.2649879473738325</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>62292</v>
+        <v>71882</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>51710</v>
+        <v>59672</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>74967</v>
+        <v>84547</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.2342895536819191</v>
+        <v>0.2289158214085625</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.1944908488942041</v>
+        <v>0.190034068998459</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.2819654539479931</v>
+        <v>0.2692514208372688</v>
       </c>
     </row>
     <row r="11">
@@ -1234,67 +1234,67 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>147</v>
+        <v>173</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>100896</v>
+        <v>119373</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>91606</v>
+        <v>109021</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>108509</v>
+        <v>127691</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.7533466088792098</v>
+        <v>0.7565589771431693</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.6839854931749129</v>
+        <v>0.6909493235743365</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.8101904717169044</v>
+        <v>0.8092776091622069</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>145</v>
+        <v>173</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>102687</v>
+        <v>122754</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>94651</v>
+        <v>114827</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>109680</v>
+        <v>132037</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.7782604336213694</v>
+        <v>0.7857543498892362</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.7173596930849763</v>
+        <v>0.7350120526261676</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.8312646590896197</v>
+        <v>0.8451722434874211</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>292</v>
+        <v>346</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>203582</v>
+        <v>242127</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>190907</v>
+        <v>229462</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>214164</v>
+        <v>254337</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>0.7657104463180808</v>
+        <v>0.7710841785914375</v>
       </c>
       <c r="V11" s="6" t="n">
-        <v>0.7180345460520069</v>
+        <v>0.7307485791627312</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>0.8055091511057959</v>
+        <v>0.8099659310015408</v>
       </c>
     </row>
     <row r="12">
@@ -1305,16 +1305,16 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>194</v>
+        <v>227</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>133930</v>
+        <v>157784</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>133930</v>
+        <v>157784</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>133930</v>
+        <v>157784</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>1</v>
@@ -1326,16 +1326,16 @@
         <v>1</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>188</v>
+        <v>222</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>131944</v>
+        <v>156225</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>131944</v>
+        <v>156225</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>131944</v>
+        <v>156225</v>
       </c>
       <c r="N12" s="6" t="n">
         <v>1</v>
@@ -1347,16 +1347,16 @@
         <v>1</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>382</v>
+        <v>449</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>265874</v>
+        <v>314009</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>265874</v>
+        <v>314009</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>265874</v>
+        <v>314009</v>
       </c>
       <c r="U12" s="6" t="n">
         <v>1</v>
@@ -1380,67 +1380,67 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>12476</v>
+        <v>13048</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>7694</v>
+        <v>8176</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>18387</v>
+        <v>19537</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.080827249226728</v>
+        <v>0.07399163441914862</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.04984710812402083</v>
+        <v>0.04636799115582752</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.1191241694933287</v>
+        <v>0.1107898403208788</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>7948</v>
+        <v>10550</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>3781</v>
+        <v>6064</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>13899</v>
+        <v>17003</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.05319632420628293</v>
+        <v>0.06157290580377987</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.02530868218253929</v>
+        <v>0.03539419407378353</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.09303268994320174</v>
+        <v>0.09923622256413969</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>20424</v>
+        <v>23597</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>14438</v>
+        <v>16682</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>28245</v>
+        <v>33488</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.06723689362114714</v>
+        <v>0.06787159752048272</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.0475329358675274</v>
+        <v>0.04798125771210714</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.09298774795352301</v>
+        <v>0.09632105641957162</v>
       </c>
     </row>
     <row r="14">
@@ -1451,67 +1451,67 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>209</v>
+        <v>240</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>141876</v>
+        <v>163291</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>135965</v>
+        <v>156802</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>146658</v>
+        <v>168163</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.919172750773272</v>
+        <v>0.9260083655808514</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.8808758305066713</v>
+        <v>0.8892101596791211</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.950152891875979</v>
+        <v>0.9536320088441724</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>201</v>
+        <v>229</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>141455</v>
+        <v>160787</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>135504</v>
+        <v>154334</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>145622</v>
+        <v>165273</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.946803675793717</v>
+        <v>0.9384270941962202</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.9069673100567982</v>
+        <v>0.9007637774358598</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.9746913178174605</v>
+        <v>0.9646058059262164</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>410</v>
+        <v>469</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>283331</v>
+        <v>324078</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>275510</v>
+        <v>314187</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>289317</v>
+        <v>330993</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.9327631063788528</v>
+        <v>0.9321284024795173</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.9070122520464771</v>
+        <v>0.9036789435804287</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.9524670641324727</v>
+        <v>0.952018742287893</v>
       </c>
     </row>
     <row r="15">
@@ -1522,16 +1522,16 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>228</v>
+        <v>260</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>154352</v>
+        <v>176339</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>154352</v>
+        <v>176339</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>154352</v>
+        <v>176339</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>1</v>
@@ -1543,16 +1543,16 @@
         <v>1</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>212</v>
+        <v>243</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>149403</v>
+        <v>171337</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>149403</v>
+        <v>171337</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>149403</v>
+        <v>171337</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>1</v>
@@ -1564,16 +1564,16 @@
         <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>440</v>
+        <v>503</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>303755</v>
+        <v>347675</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>303755</v>
+        <v>347675</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>303755</v>
+        <v>347675</v>
       </c>
       <c r="U15" s="6" t="n">
         <v>1</v>
@@ -1597,67 +1597,67 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>146880</v>
+        <v>161783</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>131211</v>
+        <v>144506</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>164370</v>
+        <v>180688</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.2807150773981362</v>
+        <v>0.2584946618186473</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.2507700043450333</v>
+        <v>0.2308892092994714</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.3141416914663673</v>
+        <v>0.2887002357744994</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>109207</v>
+        <v>125336</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>94636</v>
+        <v>109860</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>124532</v>
+        <v>142704</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.218121588944378</v>
+        <v>0.2102289689071407</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.1890184602461841</v>
+        <v>0.1842705667851912</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.2487304796293391</v>
+        <v>0.2393603117884866</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>366</v>
+        <v>406</v>
       </c>
       <c r="R16" s="5" t="n">
-        <v>256087</v>
+        <v>287119</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>234026</v>
+        <v>261844</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>279500</v>
+        <v>312103</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.2501080246998801</v>
+        <v>0.2349478947396191</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.2285624377737537</v>
+        <v>0.214265771825843</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.2729750716981049</v>
+        <v>0.2553922250896048</v>
       </c>
     </row>
     <row r="17">
@@ -1668,67 +1668,67 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>544</v>
+        <v>669</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>376354</v>
+        <v>464083</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>358864</v>
+        <v>445178</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>392023</v>
+        <v>481360</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.7192849226018638</v>
+        <v>0.7415053381813527</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.6858583085336327</v>
+        <v>0.7112997642255007</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.7492299956549663</v>
+        <v>0.7691107907005286</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>560</v>
+        <v>675</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>391463</v>
+        <v>470852</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>376138</v>
+        <v>453484</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>406034</v>
+        <v>486328</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.7818784110556219</v>
+        <v>0.7897710310928593</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.751269520370661</v>
+        <v>0.7606396882115134</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.8109815397538159</v>
+        <v>0.8157294332148085</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>1104</v>
+        <v>1344</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>767817</v>
+        <v>934935</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>744404</v>
+        <v>909951</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>789878</v>
+        <v>960210</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.74989197530012</v>
+        <v>0.7650521052603809</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.7270249283018951</v>
+        <v>0.7446077749103951</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.7714375622262463</v>
+        <v>0.7857342281741569</v>
       </c>
     </row>
     <row r="18">
@@ -1739,16 +1739,16 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>752</v>
+        <v>896</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>523234</v>
+        <v>625866</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>523234</v>
+        <v>625866</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>523234</v>
+        <v>625866</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>1</v>
@@ -1760,16 +1760,16 @@
         <v>1</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>718</v>
+        <v>854</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>500670</v>
+        <v>596188</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>500670</v>
+        <v>596188</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>500670</v>
+        <v>596188</v>
       </c>
       <c r="N18" s="6" t="n">
         <v>1</v>
@@ -1781,16 +1781,16 @@
         <v>1</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>1470</v>
+        <v>1750</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>1023904</v>
+        <v>1222054</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>1023904</v>
+        <v>1222054</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>1023904</v>
+        <v>1222054</v>
       </c>
       <c r="U18" s="6" t="n">
         <v>1</v>
@@ -1862,7 +1862,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido en 2016 (tasa de respuesta: 69,19%)</t>
+          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido en 2016 (tasa de respuesta: 82,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2046,67 +2046,67 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>7265</v>
+        <v>7917</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>3946</v>
+        <v>4624</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>11413</v>
+        <v>12480</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.2832274296194011</v>
+        <v>0.2572268008287363</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.1538181667161357</v>
+        <v>0.1502421146051437</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.4449351694028761</v>
+        <v>0.405451195420384</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>8791</v>
+        <v>10235</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>5297</v>
+        <v>6570</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>13227</v>
+        <v>14280</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.3145402589494746</v>
+        <v>0.3212775820332013</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.1895328810031817</v>
+        <v>0.2062544886468149</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.4732632252467629</v>
+        <v>0.4482704268390983</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>16056</v>
+        <v>18152</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>10840</v>
+        <v>12446</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>21696</v>
+        <v>24241</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.2995547830709954</v>
+        <v>0.2898026806463069</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.2022416171516465</v>
+        <v>0.1986979154969956</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.4047862086542425</v>
+        <v>0.3870177826040014</v>
       </c>
     </row>
     <row r="5">
@@ -2117,67 +2117,67 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>18386</v>
+        <v>22863</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>14238</v>
+        <v>18300</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>21705</v>
+        <v>26156</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.7167725703805989</v>
+        <v>0.7427731991712637</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.5550648305971239</v>
+        <v>0.594548804579616</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.8461818332838643</v>
+        <v>0.8497578853948563</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>19157</v>
+        <v>21621</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>14721</v>
+        <v>17576</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>22651</v>
+        <v>25286</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.6854597410505254</v>
+        <v>0.6787224179667987</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.5267367747532364</v>
+        <v>0.5517295731609018</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.8104671189968183</v>
+        <v>0.7937455113531852</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>37542</v>
+        <v>44484</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>31902</v>
+        <v>38395</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>42758</v>
+        <v>50190</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.7004452169290045</v>
+        <v>0.710197319353693</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.5952137913457576</v>
+        <v>0.6129822173959986</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.7977583828483537</v>
+        <v>0.8013020845030043</v>
       </c>
     </row>
     <row r="6">
@@ -2188,16 +2188,16 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>25651</v>
+        <v>30780</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>25651</v>
+        <v>30780</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>25651</v>
+        <v>30780</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>1</v>
@@ -2209,16 +2209,16 @@
         <v>1</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>27948</v>
+        <v>31856</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>27948</v>
+        <v>31856</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>27948</v>
+        <v>31856</v>
       </c>
       <c r="N6" s="6" t="n">
         <v>1</v>
@@ -2230,16 +2230,16 @@
         <v>1</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>53598</v>
+        <v>62636</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>53598</v>
+        <v>62636</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>53598</v>
+        <v>62636</v>
       </c>
       <c r="U6" s="6" t="n">
         <v>1</v>
@@ -2263,67 +2263,67 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>57478</v>
+        <v>64891</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>47633</v>
+        <v>54353</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>69113</v>
+        <v>77488</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.2885471850027521</v>
+        <v>0.2581762177825583</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.2391233356538875</v>
+        <v>0.2162493728515869</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.3469579138239481</v>
+        <v>0.308296415538077</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>36542</v>
+        <v>38841</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>29049</v>
+        <v>30873</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>44789</v>
+        <v>48993</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.2219562012705778</v>
+        <v>0.1935928051222673</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.176444785929165</v>
+        <v>0.1538786674634725</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.2720500525574621</v>
+        <v>0.2441935050590051</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>94019</v>
+        <v>103732</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>80677</v>
+        <v>90875</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>107338</v>
+        <v>120437</v>
       </c>
       <c r="U7" s="6" t="n">
-        <v>0.2584147074998855</v>
+        <v>0.2295078115694208</v>
       </c>
       <c r="V7" s="6" t="n">
-        <v>0.2217433661989985</v>
+        <v>0.2010617234559971</v>
       </c>
       <c r="W7" s="6" t="n">
-        <v>0.2950228232018943</v>
+        <v>0.2664679053589573</v>
       </c>
     </row>
     <row r="8">
@@ -2334,67 +2334,67 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>211</v>
+        <v>275</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>141719</v>
+        <v>186453</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>130084</v>
+        <v>173856</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>151564</v>
+        <v>196991</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.7114528149972479</v>
+        <v>0.7418237822174417</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.6530420861760523</v>
+        <v>0.6917035844619224</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.760876664346113</v>
+        <v>0.783750627148413</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>202</v>
+        <v>256</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>128092</v>
+        <v>161789</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>119845</v>
+        <v>151637</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>135585</v>
+        <v>169757</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.7780437987294222</v>
+        <v>0.8064071948777327</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.7279499474425383</v>
+        <v>0.7558064949409949</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.8235552140708353</v>
+        <v>0.8461213325365274</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>413</v>
+        <v>531</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>269812</v>
+        <v>348243</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>256493</v>
+        <v>331538</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>283154</v>
+        <v>361100</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.7415852925001144</v>
+        <v>0.7704921884305792</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.704977176798106</v>
+        <v>0.7335320946410427</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.7782566338010017</v>
+        <v>0.7989382765440028</v>
       </c>
     </row>
     <row r="9">
@@ -2405,16 +2405,16 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>295</v>
+        <v>370</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>199197</v>
+        <v>251344</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>199197</v>
+        <v>251344</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>199197</v>
+        <v>251344</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
@@ -2426,16 +2426,16 @@
         <v>1</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>260</v>
+        <v>318</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>164634</v>
+        <v>200630</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>164634</v>
+        <v>200630</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>164634</v>
+        <v>200630</v>
       </c>
       <c r="N9" s="6" t="n">
         <v>1</v>
@@ -2447,16 +2447,16 @@
         <v>1</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>555</v>
+        <v>688</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>363831</v>
+        <v>451975</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>363831</v>
+        <v>451975</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>363831</v>
+        <v>451975</v>
       </c>
       <c r="U9" s="6" t="n">
         <v>1</v>
@@ -2480,67 +2480,67 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>39316</v>
+        <v>43423</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>30605</v>
+        <v>34555</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>48537</v>
+        <v>53886</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.2565376234083049</v>
+        <v>0.2409940306333904</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.1997004141018087</v>
+        <v>0.191780472690145</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.3167037037431532</v>
+        <v>0.2990647802735201</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>14467</v>
+        <v>16974</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>9049</v>
+        <v>11413</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>21219</v>
+        <v>24605</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.09409214674039533</v>
+        <v>0.09263003690487182</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.05885226973465545</v>
+        <v>0.06228224287155674</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.1380036699438708</v>
+        <v>0.1342748349630047</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>53783</v>
+        <v>60396</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>43321</v>
+        <v>49358</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>66821</v>
+        <v>73406</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.1751828127629845</v>
+        <v>0.1661868289436737</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.1411050766469618</v>
+        <v>0.1358130183699174</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.2176493818895979</v>
+        <v>0.2019844890877704</v>
       </c>
     </row>
     <row r="11">
@@ -2551,67 +2551,67 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>160</v>
+        <v>192</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>113941</v>
+        <v>136758</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>104720</v>
+        <v>126295</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>122652</v>
+        <v>145626</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.743462376591695</v>
+        <v>0.7590059693666097</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.6832962962568467</v>
+        <v>0.7009352197264799</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.8002995858981912</v>
+        <v>0.808219527309855</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>198</v>
+        <v>238</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>139289</v>
+        <v>166270</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>132537</v>
+        <v>158639</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>144707</v>
+        <v>171831</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.9059078532596047</v>
+        <v>0.9073699630951282</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.8619963300561292</v>
+        <v>0.8657251650369953</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.9411477302653446</v>
+        <v>0.9377177571284432</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>358</v>
+        <v>430</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>253230</v>
+        <v>303029</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>240192</v>
+        <v>290019</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>263692</v>
+        <v>314067</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>0.8248171872370155</v>
+        <v>0.8338131710563264</v>
       </c>
       <c r="V11" s="6" t="n">
-        <v>0.7823506181104022</v>
+        <v>0.7980155109122296</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>0.8588949233530383</v>
+        <v>0.8641869816300826</v>
       </c>
     </row>
     <row r="12">
@@ -2622,16 +2622,16 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>214</v>
+        <v>252</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>153257</v>
+        <v>180181</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>153257</v>
+        <v>180181</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>153257</v>
+        <v>180181</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>1</v>
@@ -2643,16 +2643,16 @@
         <v>1</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>219</v>
+        <v>263</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>153756</v>
+        <v>183244</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>153756</v>
+        <v>183244</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>153756</v>
+        <v>183244</v>
       </c>
       <c r="N12" s="6" t="n">
         <v>1</v>
@@ -2664,16 +2664,16 @@
         <v>1</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>433</v>
+        <v>515</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>307013</v>
+        <v>363425</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>307013</v>
+        <v>363425</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>307013</v>
+        <v>363425</v>
       </c>
       <c r="U12" s="6" t="n">
         <v>1</v>
@@ -2697,25 +2697,25 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>8509</v>
+        <v>11751</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>4347</v>
+        <v>6605</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>14296</v>
+        <v>18935</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.05823098592722193</v>
+        <v>0.0694514924124997</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.02975104541224738</v>
+        <v>0.03903763107413056</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.0978388579936252</v>
+        <v>0.1119145426842672</v>
       </c>
       <c r="J13" s="5" t="n">
         <v>11</v>
@@ -2724,40 +2724,40 @@
         <v>8014</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>4149</v>
+        <v>4003</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>13741</v>
+        <v>13595</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.05689523942120527</v>
+        <v>0.04954421353677042</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.02945679381882823</v>
+        <v>0.02474417308268423</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.09754602349237416</v>
+        <v>0.08404285300405875</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>16523</v>
+        <v>19765</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>10868</v>
+        <v>13419</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>24471</v>
+        <v>27817</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.0575753420851997</v>
+        <v>0.05972142413707508</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.03787212251384846</v>
+        <v>0.04054517777870456</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.08527199601319911</v>
+        <v>0.08405054800135528</v>
       </c>
     </row>
     <row r="14">
@@ -2768,67 +2768,67 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>137608</v>
+        <v>157445</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>131821</v>
+        <v>150261</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>141770</v>
+        <v>162591</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.941769014072778</v>
+        <v>0.9305485075875003</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.9021611420063748</v>
+        <v>0.888085457315732</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.9702489545877526</v>
+        <v>0.9609623689258693</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>190</v>
+        <v>220</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>132848</v>
+        <v>153748</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>127121</v>
+        <v>148167</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>136713</v>
+        <v>157759</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.9431047605787948</v>
+        <v>0.9504557864632296</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.9024539765076265</v>
+        <v>0.9159571469959412</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.970543206181172</v>
+        <v>0.9752558269173158</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>375</v>
+        <v>433</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>270455</v>
+        <v>311193</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>262507</v>
+        <v>303141</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>276110</v>
+        <v>317539</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.9424246579148003</v>
+        <v>0.940278575862925</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.9147280039868011</v>
+        <v>0.9159494519986445</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.9621278774861516</v>
+        <v>0.9594548222212952</v>
       </c>
     </row>
     <row r="15">
@@ -2839,16 +2839,16 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>197</v>
+        <v>228</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>146117</v>
+        <v>169196</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>146117</v>
+        <v>169196</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>146117</v>
+        <v>169196</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>1</v>
@@ -2860,16 +2860,16 @@
         <v>1</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>201</v>
+        <v>231</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>140862</v>
+        <v>161762</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>140862</v>
+        <v>161762</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>140862</v>
+        <v>161762</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>1</v>
@@ -2881,16 +2881,16 @@
         <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>398</v>
+        <v>459</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>286978</v>
+        <v>330958</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>286978</v>
+        <v>330958</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>286978</v>
+        <v>330958</v>
       </c>
       <c r="U15" s="6" t="n">
         <v>1</v>
@@ -2914,67 +2914,67 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>112567</v>
+        <v>127982</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>98079</v>
+        <v>111616</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>130076</v>
+        <v>144654</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.2147325958129284</v>
+        <v>0.2026631501550434</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.1870940664698035</v>
+        <v>0.176747335080706</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.2481324942288383</v>
+        <v>0.2290646092616782</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>67814</v>
+        <v>74064</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>57269</v>
+        <v>61213</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>82403</v>
+        <v>86772</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.1391908963230728</v>
+        <v>0.128250271495198</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.1175470932371663</v>
+        <v>0.10599752830818</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.1691366455307075</v>
+        <v>0.1502560382600164</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>265</v>
+        <v>296</v>
       </c>
       <c r="R16" s="5" t="n">
-        <v>180381</v>
+        <v>202045</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>161766</v>
+        <v>181848</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>201750</v>
+        <v>224291</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.1783443098308589</v>
+        <v>0.167118795285524</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.159939460990371</v>
+        <v>0.1504129073899769</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.1994719594363856</v>
+        <v>0.1855186742623794</v>
       </c>
     </row>
     <row r="17">
@@ -2985,67 +2985,67 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>584</v>
+        <v>715</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>411654</v>
+        <v>503518</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>394145</v>
+        <v>486846</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>426142</v>
+        <v>519884</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.7852674041870716</v>
+        <v>0.7973368498449566</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.7518675057711615</v>
+        <v>0.770935390738322</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.8129059335301964</v>
+        <v>0.8232526649192942</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>622</v>
+        <v>750</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>419385</v>
+        <v>503428</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>404796</v>
+        <v>490720</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>429930</v>
+        <v>516279</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.8608091036769272</v>
+        <v>0.8717497285048019</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.8308633544692922</v>
+        <v>0.8497439617399838</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.8824529067628336</v>
+        <v>0.8940024716918201</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>1206</v>
+        <v>1465</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>831040</v>
+        <v>1006948</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>809671</v>
+        <v>984702</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>849655</v>
+        <v>1027145</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.8216556901691411</v>
+        <v>0.832881204714476</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.8005280405636144</v>
+        <v>0.8144813257376206</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.8400605390096288</v>
+        <v>0.849587092610023</v>
       </c>
     </row>
     <row r="18">
@@ -3056,16 +3056,16 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>745</v>
+        <v>897</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>524221</v>
+        <v>631500</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>524221</v>
+        <v>631500</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>524221</v>
+        <v>631500</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>1</v>
@@ -3077,16 +3077,16 @@
         <v>1</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>726</v>
+        <v>864</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>487199</v>
+        <v>577492</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>487199</v>
+        <v>577492</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>487199</v>
+        <v>577492</v>
       </c>
       <c r="N18" s="6" t="n">
         <v>1</v>
@@ -3098,16 +3098,16 @@
         <v>1</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>1471</v>
+        <v>1761</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>1011421</v>
+        <v>1208993</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>1011421</v>
+        <v>1208993</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>1011421</v>
+        <v>1208993</v>
       </c>
       <c r="U18" s="6" t="n">
         <v>1</v>
@@ -3179,7 +3179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido en 2023 (tasa de respuesta: 78,24%)</t>
+          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido en 2023 (tasa de respuesta: 82,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3580,67 +3580,67 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>23017</v>
+        <v>23472</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>17219</v>
+        <v>17962</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>29666</v>
+        <v>30431</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.3290858686859495</v>
+        <v>0.3225422572098332</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.246193737888675</v>
+        <v>0.2468260291698436</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.4241578072760987</v>
+        <v>0.4181638057377529</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>13238</v>
+        <v>13807</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>8787</v>
+        <v>9742</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>18027</v>
+        <v>18516</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.2588526802764488</v>
+        <v>0.2544315480598982</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.1718214153167061</v>
+        <v>0.1795157510754685</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.3524838755224422</v>
+        <v>0.3411971094773891</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>36255</v>
+        <v>37280</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>29091</v>
+        <v>29763</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>44839</v>
+        <v>45236</v>
       </c>
       <c r="U7" s="6" t="n">
-        <v>0.2994217658549509</v>
+        <v>0.2934473894066592</v>
       </c>
       <c r="V7" s="6" t="n">
-        <v>0.2402526915423759</v>
+        <v>0.2342790527430347</v>
       </c>
       <c r="W7" s="6" t="n">
-        <v>0.3703137319397123</v>
+        <v>0.3560784962973363</v>
       </c>
     </row>
     <row r="8">
@@ -3651,67 +3651,67 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>46925</v>
+        <v>49300</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>40276</v>
+        <v>42341</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>52723</v>
+        <v>54810</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.6709141313140509</v>
+        <v>0.6774577427901669</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.575842192723901</v>
+        <v>0.5818361942622472</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.7538062621113246</v>
+        <v>0.7531739708301566</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>37904</v>
+        <v>40461</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>33115</v>
+        <v>35752</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>42355</v>
+        <v>44526</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.7411473197235511</v>
+        <v>0.7455684519401017</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.6475161244775575</v>
+        <v>0.658802890522611</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.8281785846832938</v>
+        <v>0.8204842489245314</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>84829</v>
+        <v>89760</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>76245</v>
+        <v>81804</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>91993</v>
+        <v>97277</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.7005782341450491</v>
+        <v>0.7065526105933407</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.6296862680602878</v>
+        <v>0.6439215037026637</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.7597473084576239</v>
+        <v>0.7657209472569654</v>
       </c>
     </row>
     <row r="9">
@@ -3722,16 +3722,16 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>69942</v>
+        <v>72772</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>69942</v>
+        <v>72772</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>69942</v>
+        <v>72772</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
@@ -3743,16 +3743,16 @@
         <v>1</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>51142</v>
+        <v>54268</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>51142</v>
+        <v>54268</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>51142</v>
+        <v>54268</v>
       </c>
       <c r="N9" s="6" t="n">
         <v>1</v>
@@ -3764,16 +3764,16 @@
         <v>1</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>121084</v>
+        <v>127040</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>121084</v>
+        <v>127040</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>121084</v>
+        <v>127040</v>
       </c>
       <c r="U9" s="6" t="n">
         <v>1</v>
@@ -3803,61 +3803,61 @@
         <v>23104</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>16509</v>
+        <v>16340</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>31085</v>
+        <v>30981</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.2482736025567329</v>
+        <v>0.2326361868811115</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.1774091275086271</v>
+        <v>0.1645357281670542</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.3340401987738181</v>
+        <v>0.3119519018980396</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>8348</v>
+        <v>9677</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>4752</v>
+        <v>5592</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>13833</v>
+        <v>15464</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.1208374846351199</v>
+        <v>0.1276393480827268</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.06879504442816714</v>
+        <v>0.07375604251557186</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.2002405892402433</v>
+        <v>0.2039772044199739</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>31451</v>
+        <v>32780</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>23532</v>
+        <v>24120</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>41798</v>
+        <v>41886</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.1939773291547254</v>
+        <v>0.187182477123139</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.1451356893385952</v>
+        <v>0.1377312016829463</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.2577918967984325</v>
+        <v>0.2391809210858375</v>
       </c>
     </row>
     <row r="11">
@@ -3868,67 +3868,67 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>69953</v>
+        <v>76208</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>61972</v>
+        <v>68331</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>76548</v>
+        <v>82972</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.7517263974432673</v>
+        <v>0.7673638131188885</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.6659598012261817</v>
+        <v>0.6880480981019602</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.822590872491373</v>
+        <v>0.8354642718329458</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>60734</v>
+        <v>66135</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>55249</v>
+        <v>60348</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>64330</v>
+        <v>70220</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.8791625153648799</v>
+        <v>0.8723606519172733</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.7997594107597567</v>
+        <v>0.7960227955800258</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.9312049555718331</v>
+        <v>0.9262439574844281</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>130688</v>
+        <v>142344</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>120341</v>
+        <v>133238</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>138607</v>
+        <v>151004</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>0.8060226708452746</v>
+        <v>0.8128175228768609</v>
       </c>
       <c r="V11" s="6" t="n">
-        <v>0.7422081032015675</v>
+        <v>0.7608190789141623</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>0.8548643106614047</v>
+        <v>0.8622687983170536</v>
       </c>
     </row>
     <row r="12">
@@ -3939,16 +3939,16 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>93057</v>
+        <v>99312</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>93057</v>
+        <v>99312</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>93057</v>
+        <v>99312</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>1</v>
@@ -3960,16 +3960,16 @@
         <v>1</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>69082</v>
+        <v>75812</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>69082</v>
+        <v>75812</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>69082</v>
+        <v>75812</v>
       </c>
       <c r="N12" s="6" t="n">
         <v>1</v>
@@ -3981,16 +3981,16 @@
         <v>1</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>209</v>
+        <v>225</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>162139</v>
+        <v>175124</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>162139</v>
+        <v>175124</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>162139</v>
+        <v>175124</v>
       </c>
       <c r="U12" s="6" t="n">
         <v>1</v>
@@ -4020,19 +4020,19 @@
         <v>11749</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>6549</v>
+        <v>6341</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>19085</v>
+        <v>19581</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.09441337617975107</v>
+        <v>0.0904011504941301</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.05262837504876525</v>
+        <v>0.04878902691420154</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.1533677109060974</v>
+        <v>0.1506679314746833</v>
       </c>
       <c r="J13" s="5" t="n">
         <v>6</v>
@@ -4041,19 +4041,19 @@
         <v>4394</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>1773</v>
+        <v>1721</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>9291</v>
+        <v>9524</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.04249989293498888</v>
+        <v>0.04147029969009031</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.01715058934460361</v>
+        <v>0.01623928865980547</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.08986977284869249</v>
+        <v>0.08988587078104367</v>
       </c>
       <c r="Q13" s="5" t="n">
         <v>19</v>
@@ -4062,19 +4062,19 @@
         <v>16143</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>9403</v>
+        <v>10023</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>25036</v>
+        <v>25524</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.07085537596189626</v>
+        <v>0.06842568711204067</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.04127432894051737</v>
+        <v>0.04248606343901008</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.109892033086651</v>
+        <v>0.1081917348644771</v>
       </c>
     </row>
     <row r="14">
@@ -4085,67 +4085,67 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>112691</v>
+        <v>118214</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>105355</v>
+        <v>110382</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>117891</v>
+        <v>123622</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.9055866238202489</v>
+        <v>0.9095988495058699</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.8466322890939025</v>
+        <v>0.8493320685253167</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.9473716249512349</v>
+        <v>0.9512109730857985</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>98992</v>
+        <v>101559</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>94095</v>
+        <v>96429</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>101613</v>
+        <v>104232</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.9575001070650112</v>
+        <v>0.9585297003099097</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.9101302271513074</v>
+        <v>0.9101141292189562</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.9828494106553963</v>
+        <v>0.9837607113401945</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>211683</v>
+        <v>219773</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>202790</v>
+        <v>210392</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>218423</v>
+        <v>225893</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.9291446240381037</v>
+        <v>0.9315743128879593</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.8901079669133496</v>
+        <v>0.8918082651355237</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.9587256710594828</v>
+        <v>0.9575139365609899</v>
       </c>
     </row>
     <row r="15">
@@ -4156,16 +4156,16 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>124440</v>
+        <v>129963</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>124440</v>
+        <v>129963</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>124440</v>
+        <v>129963</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>1</v>
@@ -4177,16 +4177,16 @@
         <v>1</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>103386</v>
+        <v>105953</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>103386</v>
+        <v>105953</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>103386</v>
+        <v>105953</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>1</v>
@@ -4198,16 +4198,16 @@
         <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>227826</v>
+        <v>235916</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>227826</v>
+        <v>235916</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>227826</v>
+        <v>235916</v>
       </c>
       <c r="U15" s="6" t="n">
         <v>1</v>
@@ -4231,67 +4231,67 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>58938</v>
+        <v>59393</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>47575</v>
+        <v>48288</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>73107</v>
+        <v>73321</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.199577453218781</v>
+        <v>0.1916390354652999</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.1610977255455545</v>
+        <v>0.1558067116395825</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.2475552608383892</v>
+        <v>0.2365777460481445</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>27638</v>
+        <v>29537</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>20735</v>
+        <v>22057</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>36256</v>
+        <v>38734</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.1170031953429169</v>
+        <v>0.1187915259234743</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.0877790334129884</v>
+        <v>0.08870829937120299</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.153483405076763</v>
+        <v>0.1557822107223183</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="R16" s="5" t="n">
-        <v>86577</v>
+        <v>88930</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>74318</v>
+        <v>76113</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>104601</v>
+        <v>105663</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.16288063728964</v>
+        <v>0.1592113937317494</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.1398170843121347</v>
+        <v>0.136264711853671</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.1967909768119987</v>
+        <v>0.1891680988468435</v>
       </c>
     </row>
     <row r="17">
@@ -4302,67 +4302,67 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>322</v>
+        <v>341</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>236377</v>
+        <v>250530</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>222208</v>
+        <v>236602</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>247740</v>
+        <v>261635</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.8004225467812189</v>
+        <v>0.8083609645347002</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.7524447391616108</v>
+        <v>0.7634222539518554</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.8389022744544455</v>
+        <v>0.8441932883604175</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>310</v>
+        <v>326</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>208581</v>
+        <v>219105</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>199963</v>
+        <v>209908</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>215484</v>
+        <v>226585</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.8829968046570831</v>
+        <v>0.8812084740765257</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.8465165949232369</v>
+        <v>0.8442177892776818</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.9122209665870115</v>
+        <v>0.9112917006287971</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>632</v>
+        <v>667</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>444957</v>
+        <v>469635</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>426933</v>
+        <v>452902</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>457216</v>
+        <v>482452</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.83711936271036</v>
+        <v>0.8407886062682505</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.8032090231880011</v>
+        <v>0.8108319011531568</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.8601829156878655</v>
+        <v>0.8637352881463292</v>
       </c>
     </row>
     <row r="18">
@@ -4373,16 +4373,16 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>409</v>
+        <v>429</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>295315</v>
+        <v>309923</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>295315</v>
+        <v>309923</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>295315</v>
+        <v>309923</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>1</v>
@@ -4394,16 +4394,16 @@
         <v>1</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>357</v>
+        <v>376</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>236219</v>
+        <v>248642</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>236219</v>
+        <v>248642</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>236219</v>
+        <v>248642</v>
       </c>
       <c r="N18" s="6" t="n">
         <v>1</v>
@@ -4415,16 +4415,16 @@
         <v>1</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>766</v>
+        <v>805</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>531534</v>
+        <v>558565</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>531534</v>
+        <v>558565</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>531534</v>
+        <v>558565</v>
       </c>
       <c r="U18" s="6" t="n">
         <v>1</v>
